--- a/e2e-screenshots/temu-marketplace/temu-unit-inventory.xlsx
+++ b/e2e-screenshots/temu-marketplace/temu-unit-inventory.xlsx
@@ -460,7 +460,7 @@
         <v>MHL</v>
       </c>
       <c r="I2">
-        <v>100</v>
+        <v>55</v>
       </c>
       <c r="J2" t="str">
         <v>OFFICE</v>
